--- a/data/raw/q1_2026/Ventas/Marzo.xlsx
+++ b/data/raw/q1_2026/Ventas/Marzo.xlsx
@@ -6548,10 +6548,10 @@
         <v>22</v>
       </c>
       <c r="C147" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D147" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F147" s="3">
         <v>4.0</v>
